--- a/conf/resources/goods-and-services-after-deregistered-schedule.xlsx
+++ b/conf/resources/goods-and-services-after-deregistered-schedule.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10720"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10703"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emmamorton/Documents/Projects/gForms/VAT forms/Templates/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dominic.warren/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7944D289-BA7C-B44B-900A-0C61FC5AA403}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFE2D1E6-6474-3A41-BAA8-EF1AD05FEAF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="35840" windowHeight="22400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38400" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="VAT Reclaim Form" sheetId="1" r:id="rId1"/>
+    <sheet name="Cover" sheetId="2" r:id="rId1"/>
+    <sheet name="VAT Reclaim Form" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,54 +34,124 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
-  <si>
-    <t>Description of Goods</t>
-  </si>
-  <si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
+  <si>
+    <t>F1</t>
+  </si>
+  <si>
+    <t>E1</t>
+  </si>
+  <si>
+    <t>The Time of supply (tax point)</t>
+  </si>
+  <si>
+    <t>D1</t>
+  </si>
+  <si>
+    <t>You can find this on the invoice.For example, 19 3 2022.</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter the supplier's name, as it appears on the invoice.
+</t>
+  </si>
+  <si>
+    <t>The name of the person or business that supplied the goods or services (as it appears on the invoice)</t>
+  </si>
+  <si>
+    <t>B1</t>
+  </si>
+  <si>
+    <t>Describe the goods or services you want to reclaim VAT on
+Enter a brief description, like 'Dining chairs' or 'Ford Focus'.</t>
+  </si>
+  <si>
+    <t>Description of goods or services</t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>Column cell on 'Claim details’ worksheet</t>
+  </si>
+  <si>
+    <t>Notes and examples</t>
+  </si>
+  <si>
+    <t>Column name on 'Claim details’ worksheet</t>
+  </si>
+  <si>
+    <t>Time of Supply</t>
+  </si>
+  <si>
+    <t>The date the invoice or credit note was issued</t>
+  </si>
+  <si>
+    <t>Type of sales document</t>
+  </si>
+  <si>
+    <t>G1</t>
+  </si>
+  <si>
+    <t>The amount of VAT you're reclaiming on the invoice, or the amount of VAT that remains unpaid on the credit note (enter the amount in GBP)</t>
+  </si>
+  <si>
+    <t>Invoice Number or Credit Note Number</t>
+  </si>
+  <si>
+    <t>Invoice number/ Credit Note Number</t>
+  </si>
+  <si>
+    <t>You can find this on the invoice or credit note.</t>
+  </si>
+  <si>
+    <t>The time of supply is the date an invoice becomes taxable. In most cases, this is the date the invoice was issued.However, this is not always the case. To check your tax point, visit section 14 of VAT Notice 700</t>
+  </si>
+  <si>
+    <t>Invoice or Credit Note</t>
+  </si>
+  <si>
+    <t>Description of Good or Services</t>
+  </si>
+  <si>
+    <t>Enter the VAT amount to be claimed based on the supporting invoice or credit note. Credit note amounts should be entered as negative values</t>
+  </si>
+  <si>
+    <t>VAT Reclaim Form</t>
+  </si>
+  <si>
+    <t>Published by HMRC on 9 July 2026.</t>
+  </si>
+  <si>
+    <t>This worksheet contains notes to help you fill in the table on the ‘Claim details’ worksheet.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The name of the person or business that supplied the goods or services </t>
+    </r>
     <r>
       <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </rPr>
+      <t>(as it appears on the invoice or credit note)</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">Type of sales document </t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </rPr>
       <t>(invoice, or credit note)</t>
     </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">The name of the person or business that supplied the goods or services </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(as it appears on the invoice or credit note)</t>
-    </r>
-  </si>
-  <si>
-    <t>The date the invoice or credit note was issuedwas issued</t>
   </si>
   <si>
     <r>
@@ -88,10 +159,9 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </rPr>
       <t>(enter the amount in GBP)</t>
     </r>
@@ -101,7 +171,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -110,28 +180,82 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
+      <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <color indexed="8"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color indexed="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0B0C0C"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color indexed="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="9"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -139,23 +263,208 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="10"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="10"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="10"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{1D8DE468-AF24-4049-95AE-C197458D9C55}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color indexed="8"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor indexed="9"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color indexed="8"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor indexed="9"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color indexed="8"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor indexed="9"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color indexed="8"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color indexed="8"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -166,6 +475,22 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{63C6995B-2C67-49BE-A101-FBE7BEE47DEC}" name="NotesTable" displayName="NotesTable" ref="A3:C10" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
+  <autoFilter ref="A3:C10" xr:uid="{02D23C97-5724-4035-ABFD-053F6EC6ADA9}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{EC64CF77-8644-4AA2-AED4-62096FDD7E98}" name="Column name on 'Claim details’ worksheet" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{68AA6B9B-58C0-435F-BAAD-B1ED5C3805B0}" name="Notes and examples" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{53FEC9E7-954A-4712-B03C-DFC9280FC815}" name="Column cell on 'Claim details’ worksheet" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -452,32 +777,215 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE20D863-C1FE-4BA4-B947-BF0214F0F4AF}">
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="46.83203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="73.5" style="3" customWidth="1"/>
+    <col min="3" max="3" width="25.5" style="2" customWidth="1"/>
+    <col min="4" max="4" width="25.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="26.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8.83203125" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.83203125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="4"/>
+    </row>
+    <row r="2" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="11"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="4"/>
+    </row>
+    <row r="3" spans="1:6" ht="34" x14ac:dyDescent="0.15">
+      <c r="A3" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="4"/>
+    </row>
+    <row r="4" spans="1:6" ht="50" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:6" ht="71.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:6" ht="64.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:6" ht="65" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="1:6" ht="65" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="4"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="4"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
+  </headerFooter>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="38.33203125" customWidth="1"/>
-    <col min="2" max="2" width="20.5" customWidth="1"/>
-    <col min="3" max="3" width="31.83203125" customWidth="1"/>
-    <col min="4" max="4" width="20.6640625" customWidth="1"/>
-    <col min="5" max="5" width="28.33203125" customWidth="1"/>
+    <col min="1" max="1" width="31.83203125" customWidth="1"/>
+    <col min="2" max="2" width="15.6640625" customWidth="1"/>
+    <col min="3" max="3" width="20.5" customWidth="1"/>
+    <col min="4" max="5" width="20.6640625" customWidth="1"/>
+    <col min="6" max="6" width="28.33203125" customWidth="1"/>
+    <col min="7" max="7" width="38.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
+    <row r="1" spans="1:7" s="26" customFormat="1" ht="102" x14ac:dyDescent="0.2">
+      <c r="A1" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" s="25" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -793,4 +1301,10 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{f9af038e-07b4-4369-a678-c835687cb272}" enabled="1" method="Standard" siteId="{ac52f73c-fd1a-4a9a-8e7a-4a248f3139e1}" contentBits="2" removed="0"/>
+</clbl:labelList>
 </file>